--- a/Reports/Lobewise Comparisons/ResultsFinal/tib.xlsx
+++ b/Reports/Lobewise Comparisons/ResultsFinal/tib.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c2d16a148962151/Desktop/BIOSTAT/Thesis/Thesis/Reports/Lobewise Comparisons/ResultsFinal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="11_F25DC773A252ABDACC1048CA799F592E5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3332516-AA14-47A6-BAA2-9B86A61A27E6}"/>
+  <xr:revisionPtr revIDLastSave="332" documentId="11_F25DC773A252ABDACC1048CA799F592E5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A97EDEA-37E2-459E-9EE2-C93E929F1052}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="25">
   <si>
     <t>Comparison</t>
   </si>
@@ -78,84 +78,6 @@
     <t>RUL vs LLS</t>
   </si>
   <si>
-    <t>LLL 1|2 vs LUS 1|2</t>
-  </si>
-  <si>
-    <t>LLS 1|2 vs LUS 1|2</t>
-  </si>
-  <si>
-    <t>LLL 0|1 vs LUS 0|1</t>
-  </si>
-  <si>
-    <t>RLL 1|2 vs RUL 1|2</t>
-  </si>
-  <si>
-    <t>LLS 0|1 vs LUS 0|1</t>
-  </si>
-  <si>
-    <t>RLL 0|1 vs RML 0|1</t>
-  </si>
-  <si>
-    <t>RLL 0|1 vs RUL 0|1</t>
-  </si>
-  <si>
-    <t>LLL 0|1 vs LLS 0|1</t>
-  </si>
-  <si>
-    <t>LLL 0|1 vs RML 0|1</t>
-  </si>
-  <si>
-    <t>LLL 0|1 vs RUL 0|1</t>
-  </si>
-  <si>
-    <t>LLL 1|2 vs RUL 1|2</t>
-  </si>
-  <si>
-    <t>RLL 1|2 vs RML 1|2</t>
-  </si>
-  <si>
-    <t>LLL 1|2 vs LLS 1|2</t>
-  </si>
-  <si>
-    <t>LLL 1|2 vs RML 1|2</t>
-  </si>
-  <si>
-    <t>RML 1|2 vs RUL 1|2</t>
-  </si>
-  <si>
-    <t>LLS 1|2 vs RUL 1|2</t>
-  </si>
-  <si>
-    <t>LLL 2|3 vs LUS 2|3</t>
-  </si>
-  <si>
-    <t>LLL 2|3 vs RUL 2|3</t>
-  </si>
-  <si>
-    <t>RLL 2|3 vs RUL 2|3</t>
-  </si>
-  <si>
-    <t>LLL 2|3 vs LLS 2|3</t>
-  </si>
-  <si>
-    <t>LLL 2|3 vs RML 2|3</t>
-  </si>
-  <si>
-    <t>LLS 2|3 vs LUS 2|3</t>
-  </si>
-  <si>
-    <t>RLL 2|3 vs RML 2|3</t>
-  </si>
-  <si>
-    <t>RML 2|3 vs RUL 2|3</t>
-  </si>
-  <si>
-    <t>LLS 2|3 vs RUL 2|3</t>
-  </si>
-  <si>
-    <t>LLL 2|3 vs RLL 2|3</t>
-  </si>
-  <si>
     <t>FDR_p</t>
   </si>
   <si>
@@ -186,61 +108,13 @@
     <t>RML vs RUL</t>
   </si>
   <si>
-    <t>RLL 0|1 vs LUS 0|1</t>
+    <t>LLS vs RUL</t>
   </si>
   <si>
-    <t>RUL 0|1 vs LUS 0|1</t>
+    <t>LLL vs RLL</t>
   </si>
   <si>
-    <t>RML 0|1 vs LUS 0|1</t>
-  </si>
-  <si>
-    <t>RLL 0|1 vs LLS 0|1</t>
-  </si>
-  <si>
-    <t>RLL 0|1 vs LLL 0|1</t>
-  </si>
-  <si>
-    <t>RUL 0|1 vs LLS 0|1</t>
-  </si>
-  <si>
-    <t>RML 0|1 vs LLS 0|1</t>
-  </si>
-  <si>
-    <t>RUL 0|1 vs RML 0|1</t>
-  </si>
-  <si>
-    <t>RLL 1|2 vs LUS 1|2</t>
-  </si>
-  <si>
-    <t>RML 1|2 vs LUS 1|2</t>
-  </si>
-  <si>
-    <t>RUL 1|2 vs LUS 1|2</t>
-  </si>
-  <si>
-    <t>RLL 1|2 vs LLS 1|2</t>
-  </si>
-  <si>
-    <t>RLL 1|2 vs LLL 1|2</t>
-  </si>
-  <si>
-    <t>RML 1|2 vs LLS 1|2</t>
-  </si>
-  <si>
-    <t>RLL 2|3 vs LUS 2|3</t>
-  </si>
-  <si>
-    <t>RML 2|3 vs LUS 2|3</t>
-  </si>
-  <si>
-    <t>RLL 2|3 vs LLS 2|3</t>
-  </si>
-  <si>
-    <t>RUL 2|3 vs LUS 2|3</t>
-  </si>
-  <si>
-    <t>RML 2|3 vs LLS 2|3</t>
+    <t>RUL vs RML</t>
   </si>
 </sst>
 </file>
@@ -276,9 +150,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -294,6 +167,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -585,14 +462,14 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
@@ -615,8 +492,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
-        <v>40</v>
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <f>1/0.2049</f>
@@ -641,7 +518,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
@@ -664,7 +541,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
@@ -687,8 +564,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>41</v>
+      <c r="A6" t="s">
+        <v>15</v>
       </c>
       <c r="B6">
         <f>1/0.33855</f>
@@ -713,7 +590,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7">
@@ -736,8 +613,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>42</v>
+      <c r="A8" t="s">
+        <v>16</v>
       </c>
       <c r="B8">
         <f>1/0.46529</f>
@@ -762,8 +639,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>43</v>
+      <c r="A9" t="s">
+        <v>17</v>
       </c>
       <c r="B9">
         <f>1/0.5407</f>
@@ -788,8 +665,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>44</v>
+      <c r="A10" t="s">
+        <v>18</v>
       </c>
       <c r="B10">
         <f>1/0.60524</f>
@@ -814,8 +691,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>45</v>
+      <c r="A11" t="s">
+        <v>19</v>
       </c>
       <c r="B11">
         <f>1/0.62363</f>
@@ -840,8 +717,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
-        <v>46</v>
+      <c r="A12" t="s">
+        <v>20</v>
       </c>
       <c r="B12">
         <f>1/0.72471</f>
@@ -866,7 +743,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
       <c r="B13">
@@ -889,7 +766,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>10</v>
       </c>
       <c r="B14">
@@ -912,8 +789,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
-        <v>47</v>
+      <c r="A15" t="s">
+        <v>21</v>
       </c>
       <c r="B15">
         <f>1/0.86053</f>
@@ -938,7 +815,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16">
@@ -969,6 +846,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31352B40-21B4-431D-AC21-5F70B9A713D1}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="10.20703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.68359375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.68359375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
@@ -987,14 +870,14 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
@@ -1017,8 +900,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
-        <v>40</v>
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <f>1/0.20895</f>
@@ -1043,7 +926,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
@@ -1066,7 +949,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
@@ -1089,8 +972,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>41</v>
+      <c r="A6" t="s">
+        <v>15</v>
       </c>
       <c r="B6">
         <f>1/0.34343</f>
@@ -1115,7 +998,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7">
@@ -1138,8 +1021,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>42</v>
+      <c r="A8" t="s">
+        <v>16</v>
       </c>
       <c r="B8">
         <f>1/0.46954</f>
@@ -1164,8 +1047,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>43</v>
+      <c r="A9" t="s">
+        <v>17</v>
       </c>
       <c r="B9">
         <f>1/0.54517</f>
@@ -1190,8 +1073,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>44</v>
+      <c r="A10" t="s">
+        <v>18</v>
       </c>
       <c r="B10">
         <f>1/0.60841</f>
@@ -1216,8 +1099,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>45</v>
+      <c r="A11" t="s">
+        <v>19</v>
       </c>
       <c r="B11">
         <f>1/0.62729</f>
@@ -1242,8 +1125,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
-        <v>46</v>
+      <c r="A12" t="s">
+        <v>20</v>
       </c>
       <c r="B12">
         <f>1/0.72833</f>
@@ -1268,7 +1151,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
       <c r="B13">
@@ -1291,7 +1174,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>10</v>
       </c>
       <c r="B14">
@@ -1314,8 +1197,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
-        <v>47</v>
+      <c r="A15" t="s">
+        <v>21</v>
       </c>
       <c r="B15">
         <f>1/0.86127</f>
@@ -1340,7 +1223,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16">
@@ -1372,7 +1255,7 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="15.41796875" customWidth="1"/>
+    <col min="1" max="1" width="17.68359375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1392,15 +1275,15 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
-        <v>48</v>
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
       <c r="B2">
         <f>1/0.230628199632427</f>
@@ -1425,7 +1308,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3">
@@ -1448,8 +1331,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
-        <v>49</v>
+      <c r="A4" t="s">
+        <v>7</v>
       </c>
       <c r="B4">
         <f>1/0.359473558368411</f>
@@ -1474,8 +1357,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
-        <v>50</v>
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5">
         <f>1/0.386821252704903</f>
@@ -1500,8 +1383,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
+      <c r="A6" t="s">
+        <v>15</v>
       </c>
       <c r="B6">
         <v>2.1610508437955418</v>
@@ -1523,8 +1406,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>51</v>
+      <c r="A7" t="s">
+        <v>8</v>
       </c>
       <c r="B7">
         <f>1/0.498399265418703</f>
@@ -1549,7 +1432,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
       <c r="B8">
@@ -1572,8 +1455,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
+      <c r="A9" t="s">
+        <v>16</v>
       </c>
       <c r="B9">
         <v>1.558671311406572</v>
@@ -1595,8 +1478,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>52</v>
+      <c r="A10" t="s">
+        <v>9</v>
       </c>
       <c r="B10">
         <f>1/0.66312495110155</f>
@@ -1621,8 +1504,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
+      <c r="A11" t="s">
+        <v>18</v>
       </c>
       <c r="B11">
         <v>1.330509487297221</v>
@@ -1644,8 +1527,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
-        <v>53</v>
+      <c r="A12" t="s">
+        <v>11</v>
       </c>
       <c r="B12">
         <f>1/0.776840636634242</f>
@@ -1670,8 +1553,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>54</v>
+      <c r="A13" t="s">
+        <v>10</v>
       </c>
       <c r="B13">
         <f>1/0.835940394555979</f>
@@ -1696,7 +1579,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>20</v>
       </c>
       <c r="B14">
@@ -1719,8 +1602,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
-        <v>55</v>
+      <c r="A15" t="s">
+        <v>24</v>
       </c>
       <c r="B15">
         <f>1/0.929301468972403</f>
@@ -1745,8 +1628,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
+      <c r="A16" t="s">
+        <v>19</v>
       </c>
       <c r="B16">
         <v>1.0335938371598721</v>
@@ -1797,15 +1680,15 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
-        <v>56</v>
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
       <c r="B2">
         <f>1/0.0632691278305409</f>
@@ -1830,8 +1713,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <v>12.254462182569879</v>
@@ -1853,8 +1736,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
-        <v>57</v>
+      <c r="A4" t="s">
+        <v>6</v>
       </c>
       <c r="B4">
         <f>1/0.117589017031856</f>
@@ -1879,8 +1762,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
+      <c r="A5" t="s">
+        <v>15</v>
       </c>
       <c r="B5">
         <v>7.0297449656931672</v>
@@ -1902,8 +1785,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>58</v>
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6">
         <f>1/0.167105488537831</f>
@@ -1928,8 +1811,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
+      <c r="A7" t="s">
+        <v>16</v>
       </c>
       <c r="B7">
         <v>2.6411852710440962</v>
@@ -1951,8 +1834,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>59</v>
+      <c r="A8" t="s">
+        <v>8</v>
       </c>
       <c r="B8">
         <f>1/0.444765832850543</f>
@@ -1977,8 +1860,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
+      <c r="A9" t="s">
+        <v>19</v>
       </c>
       <c r="B9">
         <v>2.0477878897867119</v>
@@ -2000,8 +1883,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
+      <c r="A10" t="s">
+        <v>17</v>
       </c>
       <c r="B10">
         <v>1.858552837124684</v>
@@ -2023,8 +1906,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
+      <c r="A11" t="s">
+        <v>18</v>
       </c>
       <c r="B11">
         <v>1.7432299809416389</v>
@@ -2046,8 +1929,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
-        <v>25</v>
+      <c r="A12" t="s">
+        <v>20</v>
       </c>
       <c r="B12">
         <v>1.440990162302447</v>
@@ -2069,8 +1952,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>26</v>
+      <c r="A13" t="s">
+        <v>21</v>
       </c>
       <c r="B13">
         <v>1.4210977585819951</v>
@@ -2092,8 +1975,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
-        <v>60</v>
+      <c r="A14" t="s">
+        <v>9</v>
       </c>
       <c r="B14">
         <f>1/0.775329134323543</f>
@@ -2118,8 +2001,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
-        <v>61</v>
+      <c r="A15" t="s">
+        <v>10</v>
       </c>
       <c r="B15">
         <f>1/0.826620800500499</f>
@@ -2145,7 +2028,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>1.1747089667885131</v>
@@ -2176,7 +2059,7 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="19.62890625" customWidth="1"/>
+    <col min="1" max="1" width="10.20703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2196,15 +2079,15 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
-        <v>28</v>
+      <c r="A2" t="s">
+        <v>14</v>
       </c>
       <c r="B2">
         <v>11.961628693996429</v>
@@ -2226,8 +2109,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
-        <v>62</v>
+      <c r="A3" t="s">
+        <v>5</v>
       </c>
       <c r="B3">
         <f>1/0.10138277673112</f>
@@ -2252,8 +2135,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
+      <c r="A4" t="s">
+        <v>19</v>
       </c>
       <c r="B4">
         <v>5.3999410804503292</v>
@@ -2275,8 +2158,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>4.4528136700695136</v>
@@ -2298,8 +2181,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>31</v>
+      <c r="A6" t="s">
+        <v>18</v>
       </c>
       <c r="B6">
         <v>2.97544617685922</v>
@@ -2321,8 +2204,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>32</v>
+      <c r="A7" t="s">
+        <v>20</v>
       </c>
       <c r="B7">
         <v>2.7129591390474901</v>
@@ -2344,8 +2227,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>63</v>
+      <c r="A8" t="s">
+        <v>6</v>
       </c>
       <c r="B8">
         <f>1/0.226805162444904</f>
@@ -2370,8 +2253,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>64</v>
+      <c r="A9" t="s">
+        <v>8</v>
       </c>
       <c r="B9">
         <f>1/0.407570179106412</f>
@@ -2396,8 +2279,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>33</v>
+      <c r="A10" t="s">
+        <v>15</v>
       </c>
       <c r="B10">
         <v>4.0201126093373736</v>
@@ -2419,8 +2302,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>34</v>
+      <c r="A11" t="s">
+        <v>17</v>
       </c>
       <c r="B11">
         <v>2.2371172871544069</v>
@@ -2442,8 +2325,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
-        <v>35</v>
+      <c r="A12" t="s">
+        <v>21</v>
       </c>
       <c r="B12">
         <v>1.990424773720046</v>
@@ -2465,8 +2348,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>65</v>
+      <c r="A13" t="s">
+        <v>7</v>
       </c>
       <c r="B13">
         <f>1/0.451438614137937</f>
@@ -2491,8 +2374,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
-        <v>36</v>
+      <c r="A14" t="s">
+        <v>22</v>
       </c>
       <c r="B14">
         <v>1.8148340650377099</v>
@@ -2514,8 +2397,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
-        <v>37</v>
+      <c r="A15" t="s">
+        <v>23</v>
       </c>
       <c r="B15">
         <v>1.212703131224</v>
@@ -2537,8 +2420,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
-        <v>66</v>
+      <c r="A16" t="s">
+        <v>10</v>
       </c>
       <c r="B16">
         <f>1/0.911782293407572</f>
